--- a/output/指定訪問介護契約書_いいかいご.xlsx
+++ b/output/指定訪問介護契約書_いいかいご.xlsx
@@ -638,7 +638,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>4 サービス利用料金は１か月ごとに計算し、事業者が届ける請求書により、利用者は下記の方法により翌月26日までに支払うものとし、支払いを受けたときは領収証を発行します。</t>
+          <t>4 サービス利用料金は１か月ごとに計算し、事業者が届ける請求書により、利用者は下記の方法により重要事項説明書に定める期日までに支払うものとし、支払いを受けたときは領収証を発行します。</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>一 利用者がこの契約に定める利用料等の支払いを３か月以上遅延し、文書による支払い催告を行ったにもかかわらず、催告の日から７日以内にその支払いがなかった場合</t>
+          <t>一 利用者がこの契約に定める利用料等の支払いを３か月以上遅延し、文書による支払い催告を行ったにもかかわらず、催告の日から30日以内にその支払いがなかった場合</t>
         </is>
       </c>
     </row>

--- a/output/指定訪問介護契約書_いいかいご.xlsx
+++ b/output/指定訪問介護契約書_いいかいご.xlsx
@@ -519,7 +519,7 @@
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>本契約の有効期間は、本書に記載する契約開始年月日から始まり、利用者の要介護（支援）認定の有効期間満了日までとします。但し、契約期間満了の30日前までに利用者から文書による契約終了の申し入れがない場合には、本契約は更に同じ条件で更新されるものとし、以後も同様とします。</t>
+          <t>本契約の有効期間は、本書に記載する契約開始年月日から始まり、利用者の要介護認定の有効期間満了日までとします。但し、契約期間満了の30日前までに利用者から文書による契約終了の申し入れがない場合には、本契約は更に同じ条件で更新されるものとし、以後も同様とします。</t>
         </is>
       </c>
     </row>
